--- a/Documentation/Référence/Budget de puissant.xlsx
+++ b/Documentation/Référence/Budget de puissant.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cegepdesherbrooke-my.sharepoint.com/personal/202263904_cegepsherbrooke_qc_ca/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VSCodeProjects\Bombe\Documentation\Référence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{D33D316E-3910-4DCD-BC6A-17F37D9FD0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1976CC57-A17C-4744-8DD5-57AA4A291508}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4D6AB7-5D97-4C47-9DA6-821DE1C02116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{D4C6DD4C-331F-4CEE-BD9F-4D3A0C5B5711}"/>
   </bookViews>
@@ -368,51 +368,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -420,13 +375,58 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -771,85 +771,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
       <c r="J1" s="10"/>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="16"/>
-      <c r="M1" s="27" t="s">
+      <c r="L1" s="30"/>
+      <c r="M1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="11"/>
     </row>
     <row r="2" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="13" t="s">
+      <c r="F2" s="28"/>
+      <c r="G2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="18"/>
+      <c r="H2" s="22"/>
       <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="25">
         <f>I3+I4+I8+I9</f>
-        <v>153.30000000000001</v>
-      </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="24">
+        <v>145.62</v>
+      </c>
+      <c r="L2" s="26"/>
+      <c r="M2" s="14">
         <f>K2/12</f>
-        <v>12.775</v>
-      </c>
-      <c r="N2" s="25"/>
-      <c r="O2" s="26"/>
+        <v>12.135</v>
+      </c>
+      <c r="N2" s="15"/>
+      <c r="O2" s="11"/>
     </row>
     <row r="3" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="7">
         <v>1</v>
       </c>
       <c r="D3" s="4">
         <v>5</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="25">
         <v>3</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11">
+      <c r="F3" s="26"/>
+      <c r="G3" s="25">
         <f>E3*C3</f>
         <v>3</v>
       </c>
-      <c r="H3" s="12"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="4">
         <f>D3*G3</f>
         <v>15</v>
@@ -857,35 +857,35 @@
       <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="31" t="s">
+      <c r="L3" s="17"/>
+      <c r="M3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="31"/>
+      <c r="N3" s="20"/>
     </row>
     <row r="4" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="20"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="4">
         <v>3</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="25">
         <v>0.1</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="11">
+      <c r="F4" s="26"/>
+      <c r="G4" s="25">
         <f t="shared" ref="G4:G14" si="0">E4*C4</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="H4" s="12"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="4">
         <f>D4*G4</f>
         <v>1.5000000000000002</v>
@@ -893,115 +893,115 @@
       <c r="J4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="18">
         <f>I3+I4+I8</f>
-        <v>93.300000000000011</v>
-      </c>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21">
+        <v>85.62</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19">
         <f>K4/5</f>
-        <v>18.660000000000004</v>
-      </c>
-      <c r="N4" s="21"/>
+        <v>17.124000000000002</v>
+      </c>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="4"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
       <c r="I5" s="9"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26"/>
       <c r="I6" s="9"/>
       <c r="J6" s="3"/>
       <c r="L6">
         <f>K4/0.94</f>
-        <v>99.255319148936195</v>
+        <v>91.085106382978736</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="17"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="4">
         <v>7</v>
       </c>
       <c r="D7" s="4">
         <v>5</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
       <c r="I7" s="9"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="20"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="4">
         <v>256</v>
       </c>
       <c r="D8" s="4">
-        <v>12</v>
-      </c>
-      <c r="E8" s="17">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="11">
+        <v>5</v>
+      </c>
+      <c r="E8" s="27">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="25">
         <f t="shared" si="0"/>
-        <v>6.4</v>
-      </c>
-      <c r="H8" s="12"/>
+        <v>13.824</v>
+      </c>
+      <c r="H8" s="26"/>
       <c r="I8" s="4">
         <f>D8*G8</f>
-        <v>76.800000000000011</v>
+        <v>69.12</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L8">
         <f>L6-K4</f>
-        <v>5.9553191489361836</v>
+        <v>5.4651063829787319</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="4">
         <v>5</v>
       </c>
       <c r="D9" s="4">
         <v>12</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="27">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="11">
+      <c r="F9" s="27"/>
+      <c r="G9" s="25">
         <f>C9*(40*E9)</f>
         <v>5</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="26"/>
       <c r="I9" s="4">
         <f>D9*G9</f>
         <v>60</v>
@@ -1009,86 +1009,86 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="11">
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="26"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10">
         <f>L8/3</f>
-        <v>1.9851063829787279</v>
+        <v>1.8217021276595773</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="11">
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="11">
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="26"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="11">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="11">
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="12"/>
+      <c r="H14" s="26"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="L14">
         <f>131.1*L10 + 25</f>
-        <v>285.2474468085112</v>
+        <v>263.82514893617054</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
@@ -1100,38 +1100,6 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="A1:I1"/>
@@ -1148,6 +1116,38 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1159,14 +1159,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="31"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
